--- a/jj易教何子全python/project/20260307/1.xlsx
+++ b/jj易教何子全python/project/20260307/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16620" windowHeight="13290" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="14925" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -394,7 +394,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -415,6 +415,19 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -554,7 +567,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -566,34 +579,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
@@ -678,29 +691,35 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1018,13 +1037,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" ht="15" spans="1:3">
-      <c r="A1" s="6">
+      <c r="A1" s="9">
         <v>1</v>
       </c>
-      <c r="B1" s="6">
+      <c r="B1" s="9">
         <v>2</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="9">
         <v>3</v>
       </c>
     </row>
@@ -1049,102 +1068,133 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:4">
+    <row r="1" ht="15" customHeight="1" spans="1:5">
       <c r="A1" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:5">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="5">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:5">
+      <c r="A3" s="5">
         <v>7</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B3" s="7">
         <v>8</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:4">
-      <c r="A2" s="4">
+      <c r="C3" s="7">
         <v>9</v>
       </c>
-      <c r="B2" s="5">
+      <c r="D3" s="7">
         <v>10</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" ht="15" spans="1:5">
+      <c r="A4" s="7">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:B2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
